--- a/results/methods_summary.xlsx
+++ b/results/methods_summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soumi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\Fin_ExBERT2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E33FD9-344A-4812-97CB-9EF24270BA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87AB692-2A4B-4ABE-953F-3F40A87F7DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,12 +34,6 @@
     <t>Performance/Results</t>
   </si>
   <si>
-    <t>Expected SQuAD score</t>
-  </si>
-  <si>
-    <t>Expected FinQA-10K score</t>
-  </si>
-  <si>
     <t>Limitations</t>
   </si>
   <si>
@@ -224,6 +218,12 @@
   </si>
   <si>
     <t>Distillation into a single model; on-device ensembles.</t>
+  </si>
+  <si>
+    <t>SQuAD score</t>
+  </si>
+  <si>
+    <t>FinQA-10K score</t>
   </si>
 </sst>
 </file>
@@ -618,30 +618,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -650,24 +650,24 @@
         <v>3.2</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>3.8</v>
@@ -676,76 +676,76 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>3.5</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>4.2</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>4.5</v>
@@ -754,24 +754,24 @@
         <v>4.3</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>4.4000000000000004</v>
@@ -780,24 +780,24 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>4.8</v>
@@ -806,24 +806,24 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>4.5</v>
@@ -832,24 +832,24 @@
         <v>2.5</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>4.7</v>
@@ -858,36 +858,36 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11">
         <v>4.9000000000000004</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
